--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/32.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/32.xlsx
@@ -426,13 +426,13 @@
         <v>-9.982964188361796</v>
       </c>
       <c r="E2">
-        <v>-20.0200007443276</v>
+        <v>-20.74591965623117</v>
       </c>
       <c r="F2">
-        <v>-4.87943454914798</v>
+        <v>-4.606745112187814</v>
       </c>
       <c r="G2">
-        <v>-14.69416540745865</v>
+        <v>-15.36133137362412</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.738832922135753</v>
       </c>
       <c r="E3">
-        <v>-20.69880088418136</v>
+        <v>-21.12157016058945</v>
       </c>
       <c r="F3">
-        <v>-4.915755146291128</v>
+        <v>-4.597763124439258</v>
       </c>
       <c r="G3">
-        <v>-14.49920407010543</v>
+        <v>-14.64562618876186</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.470535567951977</v>
       </c>
       <c r="E4">
-        <v>-20.59220966298881</v>
+        <v>-21.93257457062313</v>
       </c>
       <c r="F4">
-        <v>-5.028830610242871</v>
+        <v>-4.614451414136058</v>
       </c>
       <c r="G4">
-        <v>-14.84320947818218</v>
+        <v>-14.73120710149755</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.19423510118248</v>
       </c>
       <c r="E5">
-        <v>-21.80785586797788</v>
+        <v>-22.5575990816358</v>
       </c>
       <c r="F5">
-        <v>-5.008483421727907</v>
+        <v>-4.513367396707239</v>
       </c>
       <c r="G5">
-        <v>-14.304330462209</v>
+        <v>-14.06290230766657</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.893175359435849</v>
       </c>
       <c r="E6">
-        <v>-21.30532205039869</v>
+        <v>-22.85676818847853</v>
       </c>
       <c r="F6">
-        <v>-4.745000460082454</v>
+        <v>-4.368232457532349</v>
       </c>
       <c r="G6">
-        <v>-13.62258650876135</v>
+        <v>-14.12084844151321</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.574410977050963</v>
       </c>
       <c r="E7">
-        <v>-21.88061485985912</v>
+        <v>-23.37944918691786</v>
       </c>
       <c r="F7">
-        <v>-4.335579871248799</v>
+        <v>-4.303913042174579</v>
       </c>
       <c r="G7">
-        <v>-14.38770158579724</v>
+        <v>-13.86464201168347</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.239401645075194</v>
       </c>
       <c r="E8">
-        <v>-21.94833366016982</v>
+        <v>-23.65166028799293</v>
       </c>
       <c r="F8">
-        <v>-4.103429906614236</v>
+        <v>-4.235374751634351</v>
       </c>
       <c r="G8">
-        <v>-14.66009989385955</v>
+        <v>-13.78751954280061</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.884277104445731</v>
       </c>
       <c r="E9">
-        <v>-23.06564405208233</v>
+        <v>-24.15077963617034</v>
       </c>
       <c r="F9">
-        <v>-4.204484102816554</v>
+        <v>-4.067694965224869</v>
       </c>
       <c r="G9">
-        <v>-14.29562538271349</v>
+        <v>-13.75304848737295</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.510346320519146</v>
       </c>
       <c r="E10">
-        <v>-22.03738610153066</v>
+        <v>-25.14286413634874</v>
       </c>
       <c r="F10">
-        <v>-4.338473358586777</v>
+        <v>-3.895634771989383</v>
       </c>
       <c r="G10">
-        <v>-13.44901295086459</v>
+        <v>-12.96924207022233</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.130333804609114</v>
       </c>
       <c r="E11">
-        <v>-24.13986148533785</v>
+        <v>-24.6125571876805</v>
       </c>
       <c r="F11">
-        <v>-4.643435989560012</v>
+        <v>-4.124595522123167</v>
       </c>
       <c r="G11">
-        <v>-14.37087739336666</v>
+        <v>-12.69890623203098</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.747691355080069</v>
       </c>
       <c r="E12">
-        <v>-24.81811367983667</v>
+        <v>-25.46345745372176</v>
       </c>
       <c r="F12">
-        <v>-3.548319372445815</v>
+        <v>-4.123591540830974</v>
       </c>
       <c r="G12">
-        <v>-13.40194030384169</v>
+        <v>-12.55660243202541</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.363279289999668</v>
       </c>
       <c r="E13">
-        <v>-25.08933757357807</v>
+        <v>-26.70419140471332</v>
       </c>
       <c r="F13">
-        <v>-3.71363002808329</v>
+        <v>-3.865303271168477</v>
       </c>
       <c r="G13">
-        <v>-12.83763464285414</v>
+        <v>-12.79718308690979</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.996026611007184</v>
       </c>
       <c r="E14">
-        <v>-25.71727842185168</v>
+        <v>-26.56470534832906</v>
       </c>
       <c r="F14">
-        <v>-3.779131523724856</v>
+        <v>-3.786712742195276</v>
       </c>
       <c r="G14">
-        <v>-13.14025161059892</v>
+        <v>-12.30622918343587</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.653432972598269</v>
       </c>
       <c r="E15">
-        <v>-26.28868127213953</v>
+        <v>-27.05529757995003</v>
       </c>
       <c r="F15">
-        <v>-3.622251991513074</v>
+        <v>-3.566988288602708</v>
       </c>
       <c r="G15">
-        <v>-12.47609989614696</v>
+        <v>-12.01151448789333</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.337277897203098</v>
       </c>
       <c r="E16">
-        <v>-26.40345544586394</v>
+        <v>-28.54315488601417</v>
       </c>
       <c r="F16">
-        <v>-3.281540336904623</v>
+        <v>-3.624703130657958</v>
       </c>
       <c r="G16">
-        <v>-12.61162700943364</v>
+        <v>-11.43167574723552</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.065317821077866</v>
       </c>
       <c r="E17">
-        <v>-27.70786426987735</v>
+        <v>-28.40098344454336</v>
       </c>
       <c r="F17">
-        <v>-3.572111740989023</v>
+        <v>-3.407279881710366</v>
       </c>
       <c r="G17">
-        <v>-11.59373357247393</v>
+        <v>-11.06245722433169</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.847988697930921</v>
       </c>
       <c r="E18">
-        <v>-26.96769877874565</v>
+        <v>-28.96847369328858</v>
       </c>
       <c r="F18">
-        <v>-2.92273382474942</v>
+        <v>-3.262716516043407</v>
       </c>
       <c r="G18">
-        <v>-11.26986952345811</v>
+        <v>-11.05076106694144</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.684829227132477</v>
       </c>
       <c r="E19">
-        <v>-27.54959863178328</v>
+        <v>-29.74545567810264</v>
       </c>
       <c r="F19">
-        <v>-3.196877874868902</v>
+        <v>-3.120649849728486</v>
       </c>
       <c r="G19">
-        <v>-11.42344904157043</v>
+        <v>-10.83028204457152</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.582664839640293</v>
       </c>
       <c r="E20">
-        <v>-29.12794390546869</v>
+        <v>-30.33618152698121</v>
       </c>
       <c r="F20">
-        <v>-2.405350455574099</v>
+        <v>-2.875908700571372</v>
       </c>
       <c r="G20">
-        <v>-11.18224931467021</v>
+        <v>-10.28858409907165</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.54171069974418</v>
       </c>
       <c r="E21">
-        <v>-30.55634914052313</v>
+        <v>-30.89235738341826</v>
       </c>
       <c r="F21">
-        <v>-2.545961680362301</v>
+        <v>-2.645101519496749</v>
       </c>
       <c r="G21">
-        <v>-10.28594559427686</v>
+        <v>-10.66868769570861</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.548568740852726</v>
       </c>
       <c r="E22">
-        <v>-30.38164514178122</v>
+        <v>-31.6261694255172</v>
       </c>
       <c r="F22">
-        <v>-2.234293415263404</v>
+        <v>-2.573074973823332</v>
       </c>
       <c r="G22">
-        <v>-10.0745176034113</v>
+        <v>-10.33490525225714</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.589167234779437</v>
       </c>
       <c r="E23">
-        <v>-29.46715377948725</v>
+        <v>-31.35348962738233</v>
       </c>
       <c r="F23">
-        <v>-2.440430158347853</v>
+        <v>-2.464317789142382</v>
       </c>
       <c r="G23">
-        <v>-10.32517886946276</v>
+        <v>-10.44445120415162</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.653806965703681</v>
       </c>
       <c r="E24">
-        <v>-31.86349995554819</v>
+        <v>-31.67542337306163</v>
       </c>
       <c r="F24">
-        <v>-2.407862065539387</v>
+        <v>-2.218884953203931</v>
       </c>
       <c r="G24">
-        <v>-10.91241005830976</v>
+        <v>-10.28356862257966</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.725069243592257</v>
       </c>
       <c r="E25">
-        <v>-32.23015917476424</v>
+        <v>-31.9822342797923</v>
       </c>
       <c r="F25">
-        <v>-2.16325014169711</v>
+        <v>-2.123722934337726</v>
       </c>
       <c r="G25">
-        <v>-9.615291968385758</v>
+        <v>-9.893609531872286</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.784671816076552</v>
       </c>
       <c r="E26">
-        <v>-30.6139535941377</v>
+        <v>-32.40874407573073</v>
       </c>
       <c r="F26">
-        <v>-2.111236952475329</v>
+        <v>-2.14165543187353</v>
       </c>
       <c r="G26">
-        <v>-10.91210217757461</v>
+        <v>-10.40069903430461</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.828709491331004</v>
       </c>
       <c r="E27">
-        <v>-31.16678517252009</v>
+        <v>-31.87666196525149</v>
       </c>
       <c r="F27">
-        <v>-1.953548105311013</v>
+        <v>-2.121904667888582</v>
       </c>
       <c r="G27">
-        <v>-10.30674244135456</v>
+        <v>-10.66667488402074</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.8493508476761</v>
       </c>
       <c r="E28">
-        <v>-33.03315950698937</v>
+        <v>-32.66587988683427</v>
       </c>
       <c r="F28">
-        <v>-1.812193006595097</v>
+        <v>-2.195936691044176</v>
       </c>
       <c r="G28">
-        <v>-9.804946501239526</v>
+        <v>-10.42278037305155</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.837993053389229</v>
       </c>
       <c r="E29">
-        <v>-31.96171802830056</v>
+        <v>-32.37986826122082</v>
       </c>
       <c r="F29">
-        <v>-2.046089998082162</v>
+        <v>-2.27488341800058</v>
       </c>
       <c r="G29">
-        <v>-8.995935245625668</v>
+        <v>-10.68023487854959</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.799309786459945</v>
       </c>
       <c r="E30">
-        <v>-30.77883533275698</v>
+        <v>-32.30116564720451</v>
       </c>
       <c r="F30">
-        <v>-1.960224746577577</v>
+        <v>-2.006051688035251</v>
       </c>
       <c r="G30">
-        <v>-10.23621126864038</v>
+        <v>-10.35645028262671</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.736629197758817</v>
       </c>
       <c r="E31">
-        <v>-31.33928833289428</v>
+        <v>-32.03030855985774</v>
       </c>
       <c r="F31">
-        <v>-1.72425020964429</v>
+        <v>-2.238296086553731</v>
       </c>
       <c r="G31">
-        <v>-10.92075263306872</v>
+        <v>-10.16010182669254</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.649636861915432</v>
       </c>
       <c r="E32">
-        <v>-31.20090948840489</v>
+        <v>-31.91467624030888</v>
       </c>
       <c r="F32">
-        <v>-1.58408050468178</v>
+        <v>-1.992963483071019</v>
       </c>
       <c r="G32">
-        <v>-10.14296975352681</v>
+        <v>-10.5098410996433</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.545570065040202</v>
       </c>
       <c r="E33">
-        <v>-30.8596708580309</v>
+        <v>-31.35075895755571</v>
       </c>
       <c r="F33">
-        <v>-1.945601576815957</v>
+        <v>-2.034419958111523</v>
       </c>
       <c r="G33">
-        <v>-9.895228388640991</v>
+        <v>-10.96624614986939</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.431452212073189</v>
       </c>
       <c r="E34">
-        <v>-31.122453676222</v>
+        <v>-30.88265059938282</v>
       </c>
       <c r="F34">
-        <v>-1.906923446044442</v>
+        <v>-2.228595904266949</v>
       </c>
       <c r="G34">
-        <v>-10.04442474445933</v>
+        <v>-10.51958403516538</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.308378499641836</v>
       </c>
       <c r="E35">
-        <v>-29.70650853739967</v>
+        <v>-30.77970027129244</v>
       </c>
       <c r="F35">
-        <v>-2.120252074919996</v>
+        <v>-2.18610231323814</v>
       </c>
       <c r="G35">
-        <v>-11.35439437216678</v>
+        <v>-10.65531309172996</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.177915642084164</v>
       </c>
       <c r="E36">
-        <v>-31.82822767150245</v>
+        <v>-30.47229160599275</v>
       </c>
       <c r="F36">
-        <v>-2.393560302330054</v>
+        <v>-2.169405739867313</v>
       </c>
       <c r="G36">
-        <v>-9.588446754607808</v>
+        <v>-10.87899010109082</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.045418728477419</v>
       </c>
       <c r="E37">
-        <v>-28.05441932873635</v>
+        <v>-30.34399088040744</v>
       </c>
       <c r="F37">
-        <v>-2.29256326347853</v>
+        <v>-2.084768128853677</v>
       </c>
       <c r="G37">
-        <v>-10.44663616420754</v>
+        <v>-10.79695478262768</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.909528500078336</v>
       </c>
       <c r="E38">
-        <v>-29.26139803447474</v>
+        <v>-29.57960258180871</v>
       </c>
       <c r="F38">
-        <v>-1.603199224338393</v>
+        <v>-2.121825144617913</v>
       </c>
       <c r="G38">
-        <v>-10.24443797430547</v>
+        <v>-11.24128627327204</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.765562597030072</v>
       </c>
       <c r="E39">
-        <v>-28.62348548643624</v>
+        <v>-29.4184772123788</v>
       </c>
       <c r="F39">
-        <v>-2.115969415447523</v>
+        <v>-1.961863257300314</v>
       </c>
       <c r="G39">
-        <v>-11.11475722276109</v>
+        <v>-10.91960056322106</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.617283116911406</v>
       </c>
       <c r="E40">
-        <v>-28.33024868054355</v>
+        <v>-29.18848507447724</v>
       </c>
       <c r="F40">
-        <v>-1.928234854216265</v>
+        <v>-2.111847459251193</v>
       </c>
       <c r="G40">
-        <v>-10.63895899676596</v>
+        <v>-10.95790026456488</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.463469178152025</v>
       </c>
       <c r="E41">
-        <v>-28.21691909002759</v>
+        <v>-29.08097457306113</v>
       </c>
       <c r="F41">
-        <v>-2.241525891057247</v>
+        <v>-1.978308835348093</v>
       </c>
       <c r="G41">
-        <v>-10.46955838152145</v>
+        <v>-10.81760596570165</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.300049261679841</v>
       </c>
       <c r="E42">
-        <v>-27.04932905120792</v>
+        <v>-28.7760814750727</v>
       </c>
       <c r="F42">
-        <v>-1.963936660909521</v>
+        <v>-2.100997503009324</v>
       </c>
       <c r="G42">
-        <v>-10.22961666192615</v>
+        <v>-10.9855267670901</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.130530527820184</v>
       </c>
       <c r="E43">
-        <v>-26.87607416414846</v>
+        <v>-28.27011054572169</v>
       </c>
       <c r="F43">
-        <v>-2.111999050485905</v>
+        <v>-2.095488859780708</v>
       </c>
       <c r="G43">
-        <v>-10.39198236789971</v>
+        <v>-11.21145163687213</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.956386804530065</v>
       </c>
       <c r="E44">
-        <v>-27.05006266399716</v>
+        <v>-27.42589430731575</v>
       </c>
       <c r="F44">
-        <v>-2.125956212855674</v>
+        <v>-2.033092913532238</v>
       </c>
       <c r="G44">
-        <v>-10.5656469657988</v>
+        <v>-10.78155412477899</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.776378997497417</v>
       </c>
       <c r="E45">
-        <v>-25.24997160357816</v>
+        <v>-26.81607188354683</v>
       </c>
       <c r="F45">
-        <v>-2.001619094062871</v>
+        <v>-2.060749616009505</v>
       </c>
       <c r="G45">
-        <v>-10.20004355862385</v>
+        <v>-10.876603197757</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.594030895007564</v>
       </c>
       <c r="E46">
-        <v>-25.75399981757988</v>
+        <v>-26.8789905014094</v>
       </c>
       <c r="F46">
-        <v>-1.91771707330292</v>
+        <v>-2.114186768796698</v>
       </c>
       <c r="G46">
-        <v>-10.09818800401709</v>
+        <v>-11.37285066354821</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.413903955892391</v>
       </c>
       <c r="E47">
-        <v>-24.34535457885791</v>
+        <v>-25.56784330807257</v>
       </c>
       <c r="F47">
-        <v>-2.055491139736534</v>
+        <v>-2.018086209663122</v>
       </c>
       <c r="G47">
-        <v>-10.31496252592857</v>
+        <v>-10.94616769117371</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.237091485807751</v>
       </c>
       <c r="E48">
-        <v>-24.82647324285483</v>
+        <v>-25.96670677019417</v>
       </c>
       <c r="F48">
-        <v>-1.817044754473293</v>
+        <v>-2.069913844586676</v>
       </c>
       <c r="G48">
-        <v>-10.76523975636146</v>
+        <v>-11.3607605512388</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.065164554775887</v>
       </c>
       <c r="E49">
-        <v>-24.70214398897424</v>
+        <v>-24.99665329606308</v>
       </c>
       <c r="F49">
-        <v>-2.051725381523407</v>
+        <v>-2.296425112310381</v>
       </c>
       <c r="G49">
-        <v>-10.51556834342624</v>
+        <v>-11.30870222263376</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.90445823828396</v>
       </c>
       <c r="E50">
-        <v>-23.94606544017959</v>
+        <v>-24.74766420969934</v>
       </c>
       <c r="F50">
-        <v>-2.176029365620098</v>
+        <v>-2.070071234393208</v>
       </c>
       <c r="G50">
-        <v>-10.38508981208695</v>
+        <v>-11.73428278334369</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.757838153713308</v>
       </c>
       <c r="E51">
-        <v>-24.90581663594322</v>
+        <v>-24.23907129389789</v>
       </c>
       <c r="F51">
-        <v>-1.830940617655255</v>
+        <v>-2.203195674594908</v>
       </c>
       <c r="G51">
-        <v>-11.65804423011981</v>
+        <v>-11.39847759656771</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.627130182917886</v>
       </c>
       <c r="E52">
-        <v>-23.90702999423348</v>
+        <v>-23.66785411104436</v>
       </c>
       <c r="F52">
-        <v>-1.966515368634436</v>
+        <v>-1.971198129562462</v>
       </c>
       <c r="G52">
-        <v>-10.90885784294612</v>
+        <v>-11.5633493855145</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.520897436255714</v>
       </c>
       <c r="E53">
-        <v>-21.57409151122793</v>
+        <v>-23.11436137545685</v>
       </c>
       <c r="F53">
-        <v>-1.944876755338507</v>
+        <v>-2.341569479028148</v>
       </c>
       <c r="G53">
-        <v>-10.84419295692754</v>
+        <v>-11.4396740252584</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.443988637770587</v>
       </c>
       <c r="E54">
-        <v>-22.65468503588625</v>
+        <v>-22.77210383843113</v>
       </c>
       <c r="F54">
-        <v>-2.026856963723963</v>
+        <v>-2.119021120959436</v>
       </c>
       <c r="G54">
-        <v>-11.4616759109124</v>
+        <v>-11.32265948262732</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.397478957750941</v>
       </c>
       <c r="E55">
-        <v>-22.76246724574281</v>
+        <v>-23.13041028734003</v>
       </c>
       <c r="F55">
-        <v>-2.278274754147641</v>
+        <v>-2.425846750221567</v>
       </c>
       <c r="G55">
-        <v>-11.47712291639864</v>
+        <v>-11.56229663203301</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.387284605071658</v>
       </c>
       <c r="E56">
-        <v>-21.02178976430444</v>
+        <v>-22.05187721835521</v>
       </c>
       <c r="F56">
-        <v>-1.879400939086429</v>
+        <v>-2.095775474902076</v>
       </c>
       <c r="G56">
-        <v>-11.43535707387519</v>
+        <v>-11.21608640062711</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.415809836441814</v>
       </c>
       <c r="E57">
-        <v>-22.55479595622505</v>
+        <v>-22.72261667447531</v>
       </c>
       <c r="F57">
-        <v>-2.321981075054149</v>
+        <v>-2.651582666056252</v>
       </c>
       <c r="G57">
-        <v>-10.99551799352762</v>
+        <v>-11.19983493257482</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.47980378263731</v>
       </c>
       <c r="E58">
-        <v>-20.63021714533519</v>
+        <v>-21.85069976056445</v>
       </c>
       <c r="F58">
-        <v>-2.523330682917819</v>
+        <v>-2.357721815015336</v>
       </c>
       <c r="G58">
-        <v>-11.6397501554698</v>
+        <v>-11.94602196548993</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.577985857689584</v>
       </c>
       <c r="E59">
-        <v>-21.31264459286909</v>
+        <v>-21.8245161238521</v>
       </c>
       <c r="F59">
-        <v>-2.182293479920068</v>
+        <v>-2.363829367876177</v>
       </c>
       <c r="G59">
-        <v>-11.75372561729582</v>
+        <v>-12.20586006377625</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.708147617150821</v>
       </c>
       <c r="E60">
-        <v>-20.86433925153175</v>
+        <v>-21.46533115098571</v>
       </c>
       <c r="F60">
-        <v>-2.212541315633292</v>
+        <v>-2.326199121869204</v>
       </c>
       <c r="G60">
-        <v>-12.00136435526993</v>
+        <v>-12.3622237506871</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.863066770291722</v>
       </c>
       <c r="E61">
-        <v>-20.14255936487119</v>
+        <v>-21.69306358035745</v>
       </c>
       <c r="F61">
-        <v>-2.509334587280119</v>
+        <v>-2.523612327834771</v>
       </c>
       <c r="G61">
-        <v>-11.7283999439204</v>
+        <v>-12.14268492325034</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.035854696258017</v>
       </c>
       <c r="E62">
-        <v>-18.7840262195181</v>
+        <v>-21.7396162931563</v>
       </c>
       <c r="F62">
-        <v>-2.262478616143658</v>
+        <v>-2.490213382521298</v>
       </c>
       <c r="G62">
-        <v>-11.63907480417978</v>
+        <v>-12.68972277870505</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.223391821171822</v>
       </c>
       <c r="E63">
-        <v>-21.54599685848434</v>
+        <v>-21.22234682115614</v>
       </c>
       <c r="F63">
-        <v>-2.391679908325699</v>
+        <v>-2.52397018255278</v>
       </c>
       <c r="G63">
-        <v>-11.24537810755858</v>
+        <v>-12.22557767300815</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.419231646850827</v>
       </c>
       <c r="E64">
-        <v>-20.44816343327883</v>
+        <v>-21.33942598815045</v>
       </c>
       <c r="F64">
-        <v>-2.585001807688839</v>
+        <v>-2.528560994699095</v>
       </c>
       <c r="G64">
-        <v>-11.9810376056588</v>
+        <v>-12.46394026238121</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.61510657989411</v>
       </c>
       <c r="E65">
-        <v>-18.39190565519392</v>
+        <v>-20.56549619481756</v>
       </c>
       <c r="F65">
-        <v>-2.833898047738395</v>
+        <v>-2.397074236852729</v>
       </c>
       <c r="G65">
-        <v>-12.03009326945972</v>
+        <v>-12.03156315167916</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.808204832881629</v>
       </c>
       <c r="E66">
-        <v>-20.54900802095564</v>
+        <v>-20.79332825061747</v>
       </c>
       <c r="F66">
-        <v>-2.582532444461094</v>
+        <v>-2.44033158262692</v>
       </c>
       <c r="G66">
-        <v>-12.77680336857003</v>
+        <v>-12.66879019926023</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.993350300984635</v>
       </c>
       <c r="E67">
-        <v>-18.76396055119011</v>
+        <v>-20.75890731968516</v>
       </c>
       <c r="F67">
-        <v>-2.308221892493649</v>
+        <v>-2.528638861234958</v>
       </c>
       <c r="G67">
-        <v>-12.34366152184841</v>
+        <v>-12.29875066106266</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.162181018457812</v>
       </c>
       <c r="E68">
-        <v>-21.0798629149788</v>
+        <v>-19.87479975374566</v>
       </c>
       <c r="F68">
-        <v>-2.354453077243889</v>
+        <v>-2.725627943090292</v>
       </c>
       <c r="G68">
-        <v>-11.91573378435114</v>
+        <v>-12.8133782756879</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.313000805513079</v>
       </c>
       <c r="E69">
-        <v>-19.95230458638694</v>
+        <v>-20.42018199238543</v>
       </c>
       <c r="F69">
-        <v>-2.546994654513592</v>
+        <v>-2.536758518517199</v>
       </c>
       <c r="G69">
-        <v>-11.5108904808992</v>
+        <v>-12.23237753354581</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.442873337880041</v>
       </c>
       <c r="E70">
-        <v>-19.29125606464325</v>
+        <v>-20.5855346923015</v>
       </c>
       <c r="F70">
-        <v>-2.843362973682783</v>
+        <v>-2.851620139953888</v>
       </c>
       <c r="G70">
-        <v>-12.61613266191259</v>
+        <v>-12.05846133418574</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.545736938803764</v>
       </c>
       <c r="E71">
-        <v>-18.64780066441936</v>
+        <v>-20.6469906130596</v>
       </c>
       <c r="F71">
-        <v>-2.967830974525228</v>
+        <v>-2.477404337371809</v>
       </c>
       <c r="G71">
-        <v>-11.5588569752177</v>
+        <v>-12.4713492632981</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.618776700466422</v>
       </c>
       <c r="E72">
-        <v>-21.34743233019601</v>
+        <v>-20.35619012618304</v>
       </c>
       <c r="F72">
-        <v>-2.919680462502701</v>
+        <v>-2.918853751834707</v>
       </c>
       <c r="G72">
-        <v>-11.03911125718875</v>
+        <v>-11.97454562585629</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.660067500244672</v>
       </c>
       <c r="E73">
-        <v>-20.57481579432535</v>
+        <v>-20.23054308636622</v>
       </c>
       <c r="F73">
-        <v>-2.252963159787699</v>
+        <v>-2.994735519400753</v>
       </c>
       <c r="G73">
-        <v>-11.02982848749663</v>
+        <v>-12.35187829587688</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.665414778153629</v>
       </c>
       <c r="E74">
-        <v>-19.3727006696712</v>
+        <v>-20.96450456810741</v>
       </c>
       <c r="F74">
-        <v>-2.827085554217772</v>
+        <v>-2.986406285165604</v>
       </c>
       <c r="G74">
-        <v>-11.61839382619596</v>
+        <v>-11.74707804185297</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.631182096336386</v>
       </c>
       <c r="E75">
-        <v>-20.90926171368784</v>
+        <v>-21.8202050165968</v>
       </c>
       <c r="F75">
-        <v>-2.896337069091811</v>
+        <v>-2.815186056476557</v>
       </c>
       <c r="G75">
-        <v>-12.16331624305107</v>
+        <v>-11.63441355606049</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.558247940109287</v>
       </c>
       <c r="E76">
-        <v>-22.44336379631831</v>
+        <v>-21.64262543686001</v>
       </c>
       <c r="F76">
-        <v>-2.641199080662161</v>
+        <v>-3.105051691533772</v>
       </c>
       <c r="G76">
-        <v>-11.581136946697</v>
+        <v>-12.28010235803994</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.445395243141792</v>
       </c>
       <c r="E77">
-        <v>-22.35252713619845</v>
+        <v>-21.26184869992505</v>
       </c>
       <c r="F77">
-        <v>-3.270798068425119</v>
+        <v>-2.936705069365037</v>
       </c>
       <c r="G77">
-        <v>-11.76780536747435</v>
+        <v>-11.91808096113848</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.291394819253513</v>
       </c>
       <c r="E78">
-        <v>-22.12814577759239</v>
+        <v>-22.14765444361743</v>
       </c>
       <c r="F78">
-        <v>-3.435899147109686</v>
+        <v>-2.840283932046577</v>
       </c>
       <c r="G78">
-        <v>-10.44363680994896</v>
+        <v>-11.53571957244374</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.101326991526118</v>
       </c>
       <c r="E79">
-        <v>-22.47239131470748</v>
+        <v>-21.98650416758048</v>
       </c>
       <c r="F79">
-        <v>-3.395806993181593</v>
+        <v>-3.166279639744294</v>
       </c>
       <c r="G79">
-        <v>-11.0877398606151</v>
+        <v>-11.67032966461604</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.879255565901919</v>
       </c>
       <c r="E80">
-        <v>-21.79291643222658</v>
+        <v>-23.67739560577852</v>
       </c>
       <c r="F80">
-        <v>-3.268364324995694</v>
+        <v>-3.270315130229287</v>
       </c>
       <c r="G80">
-        <v>-10.80213578639664</v>
+        <v>-11.62819966208328</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.628156220340839</v>
       </c>
       <c r="E81">
-        <v>-22.93045098905734</v>
+        <v>-23.35783930895325</v>
       </c>
       <c r="F81">
-        <v>-3.371853092994839</v>
+        <v>-3.047094137829502</v>
       </c>
       <c r="G81">
-        <v>-10.36518350175931</v>
+        <v>-11.30153158099569</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.355254175133819</v>
       </c>
       <c r="E82">
-        <v>-23.56411130000264</v>
+        <v>-23.87633599740948</v>
       </c>
       <c r="F82">
-        <v>-3.047738607668879</v>
+        <v>-3.485011393686863</v>
       </c>
       <c r="G82">
-        <v>-10.41325924408061</v>
+        <v>-11.09511244553106</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.06800097985343</v>
       </c>
       <c r="E83">
-        <v>-24.23869543055525</v>
+        <v>-24.76040280708292</v>
       </c>
       <c r="F83">
-        <v>-3.159710686240095</v>
+        <v>-3.476301110446426</v>
       </c>
       <c r="G83">
-        <v>-10.4330099587679</v>
+        <v>-11.0148714427502</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.77226961777973</v>
       </c>
       <c r="E84">
-        <v>-25.38547260283567</v>
+        <v>-25.56321520763673</v>
       </c>
       <c r="F84">
-        <v>-3.543695425603389</v>
+        <v>-3.503958641291096</v>
       </c>
       <c r="G84">
-        <v>-10.48551521102074</v>
+        <v>-10.76090956279609</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.476764440687471</v>
       </c>
       <c r="E85">
-        <v>-24.92307917886047</v>
+        <v>-26.2135040751382</v>
       </c>
       <c r="F85">
-        <v>-2.8506766294821</v>
+        <v>-3.340115852691382</v>
       </c>
       <c r="G85">
-        <v>-9.927307574916528</v>
+        <v>-10.2957448090731</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.193400733992119</v>
       </c>
       <c r="E86">
-        <v>-25.50462128245148</v>
+        <v>-27.68889449225922</v>
       </c>
       <c r="F86">
-        <v>-3.331018721873838</v>
+        <v>-3.533998556786218</v>
       </c>
       <c r="G86">
-        <v>-9.189688233857055</v>
+        <v>-10.21422593571408</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.9323894230038382</v>
       </c>
       <c r="E87">
-        <v>-28.14377970632971</v>
+        <v>-28.01556049327653</v>
       </c>
       <c r="F87">
-        <v>-3.998680363428031</v>
+        <v>-3.706654346184315</v>
       </c>
       <c r="G87">
-        <v>-8.554884505610726</v>
+        <v>-10.28540266480841</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.7045116453678494</v>
       </c>
       <c r="E88">
-        <v>-29.29320150743061</v>
+        <v>-28.7193442242306</v>
       </c>
       <c r="F88">
-        <v>-3.703681335575668</v>
+        <v>-3.550243669922518</v>
       </c>
       <c r="G88">
-        <v>-8.845997327606538</v>
+        <v>-10.23699255738765</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.5273263887348286</v>
       </c>
       <c r="E89">
-        <v>-31.42886834147701</v>
+        <v>-30.43412562705611</v>
       </c>
       <c r="F89">
-        <v>-3.413379150897179</v>
+        <v>-3.611769830398049</v>
       </c>
       <c r="G89">
-        <v>-9.344628386186024</v>
+        <v>-10.15760567535593</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.4141924147774678</v>
       </c>
       <c r="E90">
-        <v>-31.25464888945392</v>
+        <v>-31.82835673301167</v>
       </c>
       <c r="F90">
-        <v>-3.435910744253325</v>
+        <v>-3.826088358319948</v>
       </c>
       <c r="G90">
-        <v>-7.763776680273248</v>
+        <v>-10.3282510557232</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.3741067955699259</v>
       </c>
       <c r="E91">
-        <v>-31.71162852275295</v>
+        <v>-32.83969856890769</v>
       </c>
       <c r="F91">
-        <v>-3.112004179145468</v>
+        <v>-3.938102683628706</v>
       </c>
       <c r="G91">
-        <v>-8.530518890441689</v>
+        <v>-10.28915020235887</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.4211308993877194</v>
       </c>
       <c r="E92">
-        <v>-34.47066018208822</v>
+        <v>-34.17963327151127</v>
       </c>
       <c r="F92">
-        <v>-3.435522239941412</v>
+        <v>-3.719714386656853</v>
       </c>
       <c r="G92">
-        <v>-8.501333120967475</v>
+        <v>-10.52711221572168</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.5629800116722868</v>
       </c>
       <c r="E93">
-        <v>-36.00019756291896</v>
+        <v>-35.90124587737735</v>
       </c>
       <c r="F93">
-        <v>-3.815780154359511</v>
+        <v>-4.03867974020701</v>
       </c>
       <c r="G93">
-        <v>-9.537017429655231</v>
+        <v>-10.53615331558943</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.7972027512174023</v>
       </c>
       <c r="E94">
-        <v>-36.81966116239897</v>
+        <v>-37.65878513178328</v>
       </c>
       <c r="F94">
-        <v>-3.606338225337893</v>
+        <v>-3.809637810067753</v>
       </c>
       <c r="G94">
-        <v>-9.933488363438348</v>
+        <v>-10.73210450605889</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.123672525538687</v>
       </c>
       <c r="E95">
-        <v>-38.35856795595158</v>
+        <v>-39.2389621732048</v>
       </c>
       <c r="F95">
-        <v>-3.554739219817511</v>
+        <v>-4.118122659237692</v>
       </c>
       <c r="G95">
-        <v>-9.561826657926529</v>
+        <v>-10.61383526666843</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.542238999239318</v>
       </c>
       <c r="E96">
-        <v>-39.83816532542573</v>
+        <v>-40.97141594584524</v>
       </c>
       <c r="F96">
-        <v>-3.604282217444144</v>
+        <v>-4.16594513776871</v>
       </c>
       <c r="G96">
-        <v>-9.060633237099646</v>
+        <v>-10.87210085582359</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.032491585852019</v>
       </c>
       <c r="E97">
-        <v>-41.93540352904304</v>
+        <v>-42.23522700037989</v>
       </c>
       <c r="F97">
-        <v>-3.66012577753647</v>
+        <v>-4.389712852654343</v>
       </c>
       <c r="G97">
-        <v>-9.961389641243326</v>
+        <v>-10.77045717613135</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.595502857927051</v>
       </c>
       <c r="E98">
-        <v>-43.75133972001489</v>
+        <v>-44.30138855111957</v>
       </c>
       <c r="F98">
-        <v>-4.04349089808247</v>
+        <v>-4.457552829474011</v>
       </c>
       <c r="G98">
-        <v>-10.50962591418325</v>
+        <v>-11.1441614882409</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.196261453829906</v>
       </c>
       <c r="E99">
-        <v>-46.02116259653853</v>
+        <v>-46.17672020717601</v>
       </c>
       <c r="F99">
-        <v>-4.104718846292993</v>
+        <v>-4.526041417970072</v>
       </c>
       <c r="G99">
-        <v>-9.33107170220271</v>
+        <v>-11.73983787875858</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.848784337958503</v>
       </c>
       <c r="E100">
-        <v>-47.73831691974406</v>
+        <v>-47.83552740702972</v>
       </c>
       <c r="F100">
-        <v>-3.889533017700362</v>
+        <v>-4.712231073995108</v>
       </c>
       <c r="G100">
-        <v>-11.04845361670057</v>
+        <v>-11.69774760277229</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.480052925033654</v>
       </c>
       <c r="E101">
-        <v>-48.8670458588669</v>
+        <v>-49.22670971785961</v>
       </c>
       <c r="F101">
-        <v>-4.219847004668874</v>
+        <v>-4.907338933478684</v>
       </c>
       <c r="G101">
-        <v>-11.06167262503888</v>
+        <v>-11.82845125120825</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.164995687551267</v>
       </c>
       <c r="E102">
-        <v>-51.59844816616287</v>
+        <v>-52.43914691238335</v>
       </c>
       <c r="F102">
-        <v>-4.3599918586093</v>
+        <v>-4.778757260113936</v>
       </c>
       <c r="G102">
-        <v>-10.90275650751724</v>
+        <v>-12.26379461071349</v>
       </c>
     </row>
   </sheetData>
